--- a/OrderDB.xlsx
+++ b/OrderDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B80B01-9D27-4CDB-9F9F-EE2C08FDB2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B636931-7497-4300-AEE2-FE279EBAC00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="64" xr2:uid="{AE824E77-E076-4A94-A6E6-8CABB5C715EF}"/>
+    <workbookView xWindow="5115" yWindow="0" windowWidth="15375" windowHeight="7875" tabRatio="64" xr2:uid="{AE824E77-E076-4A94-A6E6-8CABB5C715EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="110">
   <si>
     <t>Product Name</t>
   </si>
@@ -375,9 +375,6 @@
     <t>DAY</t>
   </si>
   <si>
-    <t>Countery code</t>
-  </si>
-  <si>
     <t>Month</t>
   </si>
   <si>
@@ -394,9 +391,6 @@
   </si>
   <si>
     <t>LOGICAL FUNCTION</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
 </sst>
 </file>
@@ -1068,10 +1062,10 @@
         <v>97</v>
       </c>
       <c r="P1" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -1109,13 +1103,13 @@
         <v>1000</v>
       </c>
       <c r="P2" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q2" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="R2" s="24" t="s">
         <v>108</v>
-      </c>
-      <c r="R2" s="24" t="s">
-        <v>109</v>
       </c>
       <c r="T2" t="str" cm="1">
         <f t="array" ref="T2:T35">IF(D2:D35,"&gt;=$500","High price")</f>
@@ -1169,11 +1163,12 @@
       <c r="P3" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" t="str" cm="1">
+        <f t="array" ref="Q3:Q36">RIGHT(A2:A35,2)</f>
+        <v>US</v>
+      </c>
+      <c r="R3" s="26" t="s">
         <v>104</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>105</v>
       </c>
       <c r="T3" t="str">
         <v>&gt;=$500</v>
@@ -1227,8 +1222,8 @@
         <f t="array" ref="P4:P37">LEFT(A2:A35,2)</f>
         <v>28</v>
       </c>
-      <c r="Q4" t="s">
-        <v>111</v>
+      <c r="Q4" t="str">
+        <v>US</v>
       </c>
       <c r="R4" t="str" cm="1">
         <f t="array" ref="R4:R37">MID(A2:A35,4,6)</f>
@@ -1285,6 +1280,9 @@
       <c r="P5" s="3" t="str">
         <v>15</v>
       </c>
+      <c r="Q5" t="str">
+        <v>US</v>
+      </c>
       <c r="R5" t="str">
         <v>FEB-US</v>
       </c>
@@ -1332,6 +1330,9 @@
       <c r="P6" s="2" t="str">
         <v>03</v>
       </c>
+      <c r="Q6" t="str">
+        <v>US</v>
+      </c>
       <c r="R6" t="str">
         <v>MAR-US</v>
       </c>
@@ -1379,6 +1380,9 @@
       <c r="P7" s="3" t="str">
         <v>11</v>
       </c>
+      <c r="Q7" t="str">
+        <v>US</v>
+      </c>
       <c r="R7" t="str">
         <v>APR-US</v>
       </c>
@@ -1426,6 +1430,9 @@
       <c r="P8" s="2" t="str">
         <v>22</v>
       </c>
+      <c r="Q8" t="str">
+        <v>UK</v>
+      </c>
       <c r="R8" t="str">
         <v>MAY-US</v>
       </c>
@@ -1474,6 +1481,9 @@
       <c r="P9" s="3" t="str">
         <v>07</v>
       </c>
+      <c r="Q9" t="str">
+        <v>UK</v>
+      </c>
       <c r="R9" t="str">
         <v>JUN-UK</v>
       </c>
@@ -1521,6 +1531,9 @@
       <c r="P10" s="2" t="str">
         <v>19</v>
       </c>
+      <c r="Q10" t="str">
+        <v>UK</v>
+      </c>
       <c r="R10" t="str">
         <v>JUL-UK</v>
       </c>
@@ -1568,6 +1581,9 @@
       <c r="P11" s="3" t="str">
         <v>23</v>
       </c>
+      <c r="Q11" t="str">
+        <v>UK</v>
+      </c>
       <c r="R11" t="str">
         <v>AUG-UK</v>
       </c>
@@ -1615,6 +1631,9 @@
       <c r="P12" s="2" t="str">
         <v>05</v>
       </c>
+      <c r="Q12" t="str">
+        <v>UK</v>
+      </c>
       <c r="R12" t="str">
         <v>SEP-UK</v>
       </c>
@@ -1662,6 +1681,9 @@
       <c r="P13" s="3" t="str">
         <v>14</v>
       </c>
+      <c r="Q13" t="str">
+        <v>IN</v>
+      </c>
       <c r="R13" t="str">
         <v>OCT-UK</v>
       </c>
@@ -1709,6 +1731,9 @@
       <c r="P14" s="2" t="str">
         <v>17</v>
       </c>
+      <c r="Q14" t="str">
+        <v>AU</v>
+      </c>
       <c r="R14" t="str">
         <v>JUN-IN</v>
       </c>
@@ -1756,6 +1781,9 @@
       <c r="P15" s="3" t="str">
         <v>25</v>
       </c>
+      <c r="Q15" t="str">
+        <v>DE</v>
+      </c>
       <c r="R15" t="str">
         <v>NOV-AU</v>
       </c>
@@ -1803,6 +1831,9 @@
       <c r="P16" s="2" t="str">
         <v>08</v>
       </c>
+      <c r="Q16" t="str">
+        <v>CA</v>
+      </c>
       <c r="R16" t="str">
         <v>DEC-DE</v>
       </c>
@@ -1850,6 +1881,9 @@
       <c r="P17" s="3" t="str">
         <v>18</v>
       </c>
+      <c r="Q17" t="str">
+        <v>ES</v>
+      </c>
       <c r="R17" t="str">
         <v>FEB-CA</v>
       </c>
@@ -1897,6 +1931,9 @@
       <c r="P18" s="2" t="str">
         <v>16</v>
       </c>
+      <c r="Q18" t="str">
+        <v>CA</v>
+      </c>
       <c r="R18" t="str">
         <v>APR-ES</v>
       </c>
@@ -1944,6 +1981,9 @@
       <c r="P19" s="3" t="str">
         <v>21</v>
       </c>
+      <c r="Q19" t="str">
+        <v>CN</v>
+      </c>
       <c r="R19" t="str">
         <v>AUG-CA</v>
       </c>
@@ -1991,6 +2031,9 @@
       <c r="P20" s="2" t="str">
         <v>20</v>
       </c>
+      <c r="Q20" t="str">
+        <v>IT</v>
+      </c>
       <c r="R20" t="str">
         <v>AUG-CN</v>
       </c>
@@ -2038,6 +2081,9 @@
       <c r="P21" s="3" t="str">
         <v>27</v>
       </c>
+      <c r="Q21" t="str">
+        <v>UK</v>
+      </c>
       <c r="R21" t="str">
         <v>JAN-IT</v>
       </c>
@@ -2085,6 +2131,9 @@
       <c r="P22" s="2" t="str">
         <v>01</v>
       </c>
+      <c r="Q22" t="str">
+        <v>US</v>
+      </c>
       <c r="R22" t="str">
         <v>MAR-UK</v>
       </c>
@@ -2132,6 +2181,9 @@
       <c r="P23" s="3" t="str">
         <v>14</v>
       </c>
+      <c r="Q23" t="str">
+        <v>RU</v>
+      </c>
       <c r="R23" t="str">
         <v>AUG-US</v>
       </c>
@@ -2179,6 +2231,9 @@
       <c r="P24" s="2" t="str">
         <v>14</v>
       </c>
+      <c r="Q24" t="str">
+        <v>CA</v>
+      </c>
       <c r="R24" t="str">
         <v>MAY-RU</v>
       </c>
@@ -2226,6 +2281,9 @@
       <c r="P25" s="3" t="str">
         <v>09</v>
       </c>
+      <c r="Q25" t="str">
+        <v>BR</v>
+      </c>
       <c r="R25" t="str">
         <v>JAN-CA</v>
       </c>
@@ -2273,6 +2331,9 @@
       <c r="P26" s="2" t="str">
         <v>19</v>
       </c>
+      <c r="Q26" t="str">
+        <v>CA</v>
+      </c>
       <c r="R26" t="str">
         <v>JUL-BR</v>
       </c>
@@ -2320,6 +2381,9 @@
       <c r="P27" s="3" t="str">
         <v>21</v>
       </c>
+      <c r="Q27" t="str">
+        <v>CA</v>
+      </c>
       <c r="R27" t="str">
         <v>AUG-CA</v>
       </c>
@@ -2367,6 +2431,9 @@
       <c r="P28" s="2" t="str">
         <v>29</v>
       </c>
+      <c r="Q28" t="str">
+        <v>CA</v>
+      </c>
       <c r="R28" t="str">
         <v>SEP-CA</v>
       </c>
@@ -2414,6 +2481,9 @@
       <c r="P29" s="3" t="str">
         <v>03</v>
       </c>
+      <c r="Q29" t="str">
+        <v>CA</v>
+      </c>
       <c r="R29" t="str">
         <v>JUN-CA</v>
       </c>
@@ -2461,6 +2531,9 @@
       <c r="P30" s="2" t="str">
         <v>11</v>
       </c>
+      <c r="Q30" t="str">
+        <v>ES</v>
+      </c>
       <c r="R30" t="str">
         <v>JUL-CA</v>
       </c>
@@ -2508,6 +2581,9 @@
       <c r="P31" s="3" t="str">
         <v>16</v>
       </c>
+      <c r="Q31" t="str">
+        <v>CA</v>
+      </c>
       <c r="R31" t="str">
         <v>APR-ES</v>
       </c>
@@ -2555,6 +2631,9 @@
       <c r="P32" s="2" t="str">
         <v>07</v>
       </c>
+      <c r="Q32" t="str">
+        <v>CA</v>
+      </c>
       <c r="R32" t="str">
         <v>MAR-CA</v>
       </c>
@@ -2602,6 +2681,9 @@
       <c r="P33" s="3" t="str">
         <v>13</v>
       </c>
+      <c r="Q33" t="str">
+        <v>CA</v>
+      </c>
       <c r="R33" t="str">
         <v>APR-CA</v>
       </c>
@@ -2649,6 +2731,9 @@
       <c r="P34" s="2" t="str">
         <v>24</v>
       </c>
+      <c r="Q34" t="str">
+        <v>CA</v>
+      </c>
       <c r="R34" t="str">
         <v>MAY-CA</v>
       </c>
@@ -2696,6 +2781,9 @@
       <c r="P35" s="3" t="str">
         <v>02</v>
       </c>
+      <c r="Q35" t="str">
+        <v>IN</v>
+      </c>
       <c r="R35" t="str">
         <v>DEC-CA</v>
       </c>
@@ -2709,6 +2797,9 @@
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="P36" t="str">
         <v>17</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>FR</v>
       </c>
       <c r="R36" t="str">
         <v>JUN-IN</v>
@@ -2909,7 +3000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q1048576">
+  <conditionalFormatting sqref="Q5:Q1048576 Q1:Q3">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
